--- a/dist/sample-datasheet.xlsx
+++ b/dist/sample-datasheet.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+  <si>
+    <t>CODE</t>
+  </si>
   <si>
     <t>NAME</t>
   </si>
@@ -26,6 +29,9 @@
   </si>
   <si>
     <t>SPECS</t>
+  </si>
+  <si>
+    <t>AZ-DL-10W</t>
   </si>
   <si>
     <t>Azoogi LED Downlight 10W</t>
@@ -47,7 +53,10 @@
 Warranty: 3 Years</t>
   </si>
   <si>
-    <t>Azoogi LED Downlight 12W</t>
+    <t>AZ-LLL001</t>
+  </si>
+  <si>
+    <t>IP65 Series</t>
   </si>
   <si>
     <t>Architectural grade 12W recessed spotlight featuring high color rendering index and deep dimming functionality. Ideal for residential and commercial lighting.</t>
@@ -63,6 +72,9 @@
 Warranty: 3 Years</t>
   </si>
   <si>
+    <t>AZ-DL-15W</t>
+  </si>
+  <si>
     <t>Azoogi LED Downlight 15W</t>
   </si>
   <si>
@@ -79,6 +91,9 @@
 Warranty: 5 Years</t>
   </si>
   <si>
+    <t>AZ-DL-08S</t>
+  </si>
+  <si>
     <t>Azoogi LED Downlight 8W Slim</t>
   </si>
   <si>
@@ -93,6 +108,9 @@
 Cutout: 90mm
 IP Rating: IP44
 Warranty: 2 Years</t>
+  </si>
+  <si>
+    <t>AZ-DL-18H</t>
   </si>
   <si>
     <t>Azoogi LED Downlight 18W High Output</t>
@@ -177,13 +195,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -221,13 +239,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -265,13 +283,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -309,13 +327,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -353,13 +371,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -397,13 +415,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -441,13 +459,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -485,13 +503,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -529,13 +547,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -573,13 +591,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -940,17 +958,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="25" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -966,90 +985,108 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" ht="100" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" ht="100" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" ht="100" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" ht="100" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" ht="100" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" ht="100" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5" ht="100" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" ht="100" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="6" ht="100" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" ht="100" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
